--- a/output/北塩原村_KPI定義票_様式案.xlsx
+++ b/output/北塩原村_KPI定義票_様式案.xlsx
@@ -1195,7 +1195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1217,19 +1217,20 @@
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="6" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ＫＰＩの定義の案（32指標）</t>
+          <t>ＫＰＩの定義の案（38指標）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>黄色の行は他ＡＩのレビューの提案から足した指標で、基準値と目標値は村が決めます。白の行の値は正本 第４章・第３章の表によります。</t>
+          <t>黄色の行は他ＡＩのレビューの提案から足した指標で、基準値と目標値は村が決めます。白の行の値は正本 第４章・第３章の表によります。右端の「参考」は第２回のレビューが示した管理目標の案で、国が本村に指定した値ではありません。</t>
         </is>
       </c>
     </row>
@@ -1329,6 +1330,11 @@
           <t>照会・根拠</t>
         </is>
       </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>参考：レビューの目標案（Ｒ９・10・11）</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1426,6 +1432,7 @@
           <t>Ｍ-94</t>
         </is>
       </c>
+      <c r="T6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1519,6 +1526,7 @@
         </is>
       </c>
       <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -1616,6 +1624,11 @@
           <t>Ｍ-94</t>
         </is>
       </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
+          <t>100％・100％・100％</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1713,6 +1726,7 @@
           <t>Ｍ-119・Ｍ-93</t>
         </is>
       </c>
+      <c r="T9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1806,6 +1820,7 @@
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="72" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1899,6 +1914,7 @@
         </is>
       </c>
       <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="72" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1996,6 +2012,7 @@
           <t>Ｍ-140</t>
         </is>
       </c>
+      <c r="T12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="72" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -2093,6 +2110,7 @@
           <t>Ｍ-140</t>
         </is>
       </c>
+      <c r="T13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="72" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -2190,6 +2208,7 @@
           <t>Ｍ-21</t>
         </is>
       </c>
+      <c r="T14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="72" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -2279,6 +2298,11 @@
         </is>
       </c>
       <c r="S15" s="9" t="inlineStr"/>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>100％・100％・100％</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="72" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -2372,6 +2396,7 @@
           <t>Ｍ-98</t>
         </is>
       </c>
+      <c r="T16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="72" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -2461,6 +2486,7 @@
         </is>
       </c>
       <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="72" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
@@ -2558,6 +2584,11 @@
           <t>Ｍ-76・Ｍ-77</t>
         </is>
       </c>
+      <c r="T18" s="9" t="inlineStr">
+        <is>
+          <t>100％・100％・100％（３か月以内の接続）</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="72" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
@@ -2651,6 +2682,11 @@
         </is>
       </c>
       <c r="S19" s="9" t="inlineStr"/>
+      <c r="T19" s="9" t="inlineStr">
+        <is>
+          <t>２・３・４</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="72" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -2740,6 +2776,7 @@
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="72" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -2833,6 +2870,11 @@
         </is>
       </c>
       <c r="S21" s="9" t="inlineStr"/>
+      <c r="T21" s="9" t="inlineStr">
+        <is>
+          <t>０件・０件・０件</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="72" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -2926,6 +2968,7 @@
           <t>Ｍ-117</t>
         </is>
       </c>
+      <c r="T22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="72" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -3023,6 +3066,7 @@
           <t>Ｍ-115</t>
         </is>
       </c>
+      <c r="T23" s="4" t="inlineStr"/>
     </row>
     <row r="24" ht="72" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -3116,6 +3160,11 @@
           <t>Ｍ-115・Ｍ-136</t>
         </is>
       </c>
+      <c r="T24" s="9" t="inlineStr">
+        <is>
+          <t>100％・100％・100％</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="72" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -3205,6 +3254,7 @@
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr"/>
+      <c r="T25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="72" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -3294,6 +3344,7 @@
         </is>
       </c>
       <c r="S26" s="4" t="inlineStr"/>
+      <c r="T26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="72" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -3391,6 +3442,11 @@
           <t>Ｍ-22・Ｍ-87</t>
         </is>
       </c>
+      <c r="T27" s="9" t="inlineStr">
+        <is>
+          <t>80％以上・90％以上・100％</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="72" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
@@ -3484,6 +3540,11 @@
         </is>
       </c>
       <c r="S28" s="9" t="inlineStr"/>
+      <c r="T28" s="9" t="inlineStr">
+        <is>
+          <t>０件・０件・０件</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="72" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -3523,7 +3584,7 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>更新した計画も数える（更新率は別に見る）。Ｋ-31（第４次計画の策定件数）と同じ記録から取る</t>
+          <t>更新した計画も数える（更新率は別に見る）。第４次計画の指標（個別避難計画の策定件数）と同じ記録から取る</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -3581,586 +3642,605 @@
           <t>Ｍ-41・Ｍ-119</t>
         </is>
       </c>
+      <c r="T29" s="9" t="inlineStr">
+        <is>
+          <t>50％以上・75％以上・100％（優先対象者に対して）</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="72" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Ｋ-25</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>第４次計画</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>差別や偏見を感じている障がいがある人の割合</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>長期入院者の個別の退院支援の方針の作成率【提案】</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>第４章２（２）</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>％</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>分子：退院に向けた支援の方針を作成した方の数／分母：精神病床に１年以上入院している本村の方</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>方針は本人の意向の確認を含むもの</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>照会中（Ｍ-93・Ｍ-119）</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>県（保健福祉事務所）・医療機関・相談支援の記録</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P30" s="9" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q30" s="9" t="inlineStr">
+        <is>
+          <t>作成できなかった方について、本人の意向・住まい・医療の継続のどこで止まったかを分ける</t>
+        </is>
+      </c>
+      <c r="R30" s="9" t="inlineStr">
+        <is>
+          <t>丙</t>
+        </is>
+      </c>
+      <c r="S30" s="9" t="inlineStr">
+        <is>
+          <t>Ｍ-93・Ｍ-119</t>
+        </is>
+      </c>
+      <c r="T30" s="9" t="inlineStr">
+        <is>
+          <t>100％・100％・100％</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Ｋ-26</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>一般就労した方の６か月・12か月後の就労継続率【提案】</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>成果</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>第３章 ①啓発・広報</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>第４章２（３）</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>％</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>第４次障がい者計画の定義による</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>測定：測れる（参考値）</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>25.3％（第４次計画の基準値）</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>第３章に記載</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>分子：就労から６か月（12か月）後に同じ職場又は他の職場で働いている人数／分母：その時点で６か月（12か月）を経た一般就労移行者</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>対象が１人・２人のため、率ではなく継続の有無で見る年度がある</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="N31" s="9" t="inlineStr">
+        <is>
+          <t>就労定着支援事業所・ハローワークの報告</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P31" s="9" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q31" s="9" t="inlineStr">
+        <is>
+          <t>離職の理由（職場の理解・体調・通勤）を就労定着支援と共有する</t>
+        </is>
+      </c>
+      <c r="R31" s="9" t="inlineStr">
+        <is>
+          <t>丙</t>
+        </is>
+      </c>
+      <c r="S31" s="9" t="inlineStr"/>
+      <c r="T31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Ｋ-27</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>計画相談支援の月平均利用者数【提案】</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>第５章１（４）</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>各月の計画相談支援の請求の人数の年度平均</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>年度の実人数（表５-12・表５-13の数え方）とは別に数える</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>台帳 令和６〜８年度 月６人から７人程度</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>照会中（Ｍ-136）</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="inlineStr">
+        <is>
+          <t>請求の記録</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P32" s="9" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q32" s="9" t="inlineStr">
+        <is>
+          <t>国の基本指針の活動指標（月間の利用者数）と表の単位を揃える</t>
+        </is>
+      </c>
+      <c r="R32" s="9" t="inlineStr">
+        <is>
+          <t>甲</t>
+        </is>
+      </c>
+      <c r="S32" s="9" t="inlineStr">
+        <is>
+          <t>Ｍ-136</t>
+        </is>
+      </c>
+      <c r="T32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Ｋ-28</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>地域生活の選択肢と体験の機会の提示率【提案】</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>第４章２（１）（意向確認の表）</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>％</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>分子：地域での暮らしの情報と体験の機会を示した施設入所者の数／分母：年度末の施設入所者数</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Ｋ-03の意向確認の前に行うもの</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>照会中（Ｍ-94）</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>相談支援専門員・地域生活支援拠点の記録</t>
+        </is>
+      </c>
+      <c r="O33" s="9" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P33" s="9" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q33" s="9" t="inlineStr">
+        <is>
+          <t>示せなかった方について、体験の場（圏域のグループホーム・短期入所）の空きを確かめる</t>
+        </is>
+      </c>
+      <c r="R33" s="9" t="inlineStr">
+        <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="S33" s="9" t="inlineStr">
+        <is>
+          <t>Ｍ-94</t>
+        </is>
+      </c>
+      <c r="T33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Ｋ-29</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>村独自</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>見込量と実績の乖離の理由が記録されていない件数【提案】</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>第１章６（年次の点検評価）</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>サービス数</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>見込量と実績が一定以上離れたサービスのうち、理由を記録していない数</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>一定以上の幅（例：２割又は１人）は村が決める</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>15％</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>今回のアンケート（障がい者版）</t>
-        </is>
-      </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>年次の点検評価の記録</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="inlineStr">
         <is>
           <t>年１回（５月。前年度の実績）</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="P34" s="9" t="inlineStr">
         <is>
           <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>第３章の目標値の扱いは中間見直しで決める</t>
-        </is>
-      </c>
-      <c r="R30" s="4" t="inlineStr">
+      <c r="Q34" s="9" t="inlineStr">
+        <is>
+          <t>理由が書けないサービスは、翌年度の見込量の置き直しの対象にする</t>
+        </is>
+      </c>
+      <c r="R34" s="9" t="inlineStr">
         <is>
           <t>甲</t>
         </is>
       </c>
-      <c r="S30" s="4" t="inlineStr">
-        <is>
-          <t>調査の方法と集計が前回と異なるため参考値とする。正本に23.7％を記載済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="72" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>Ｋ-26</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>第４次計画</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>特定健康診査の受診率</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="S34" s="9" t="inlineStr">
+        <is>
+          <t>Ｍ-139</t>
+        </is>
+      </c>
+      <c r="T34" s="9" t="inlineStr">
+        <is>
+          <t>０件・０件・０件</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Ｋ-30</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>村独自</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>必要量に対する確保率【提案】</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>成果</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>第３章 ②保健・医療</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>第５章冒頭（必要な量・確保できる量・未充足量）</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>％</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>第４次障がい者計画の定義による</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>測定：測れる（村の記録）</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>51.3％（第４次計画の基準値）</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>第３章に記載</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>60％</t>
-        </is>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>村（国民健康保険）の記録</t>
-        </is>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>分子：実際に確保できる量／分母：必要な量（同じ単位・期間）</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>サービスごとに出し、未充足量（必要な量－確保できる量）を併せて書く</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>照会中（Ｍ-24・Ｍ-25）</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>村が決定</t>
+        </is>
+      </c>
+      <c r="N35" s="9" t="inlineStr">
+        <is>
+          <t>事業所の空き・受入条件の照会、圏域の協議</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="inlineStr">
         <is>
           <t>年１回（５月。前年度の実績）</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="P35" s="9" t="inlineStr">
         <is>
           <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
         </is>
       </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>第３章の目標値の扱いは中間見直しで決める</t>
-        </is>
-      </c>
-      <c r="R31" s="4" t="inlineStr">
+      <c r="Q35" s="9" t="inlineStr">
+        <is>
+          <t>未充足のサービスを、圏域での確保と県への意見の申出に使う</t>
+        </is>
+      </c>
+      <c r="R35" s="9" t="inlineStr">
         <is>
           <t>甲</t>
         </is>
       </c>
-      <c r="S31" s="4" t="inlineStr">
-        <is>
-          <t>照会Ｍ-96。ただしこの指標は国保の被保険者全体のもので、障がいのある方の受診率ではないことを正本に注記済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="72" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Ｋ-27</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>第４次計画</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>現在利用している福祉サービスに満足している人の割合</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>成果</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>第３章 ③福祉</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>％</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>第４次障がい者計画の定義による</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>測定：測れる（参考値）</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>52％（第４次計画の基準値）</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>第３章に記載</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>60％</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>今回のアンケート（障がい者版）</t>
-        </is>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>年１回（５月。前年度の実績）</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>第３章の目標値の扱いは中間見直しで決める</t>
-        </is>
-      </c>
-      <c r="R32" s="4" t="inlineStr">
-        <is>
-          <t>甲</t>
-        </is>
-      </c>
-      <c r="S32" s="4" t="inlineStr">
-        <is>
-          <t>分母の定義により39.4％とも61.9％とも読める。分母を決めてから評価する</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="72" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Ｋ-28</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>第４次計画</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>医療的ケア児の受入れ体制の整備</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>成果</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>第３章 ④教育・育成</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>件・有無</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>第４次障がい者計画の定義による</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>測定：測れる（村の記録）</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>無（第４次計画の基準値）</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>第３章に記載</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>有</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>村の記録</t>
-        </is>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>年１回（５月。前年度の実績）</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>第３章の目標値の扱いは中間見直しで決める</t>
-        </is>
-      </c>
-      <c r="R33" s="4" t="inlineStr">
-        <is>
-          <t>甲</t>
-        </is>
-      </c>
-      <c r="S33" s="4" t="inlineStr">
-        <is>
-          <t>照会Ｍ-95</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="72" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Ｋ-29</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>第４次計画</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>障がい者就労施設等からの物品調達件数</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>成果</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>第３章 ⑤雇用・就業</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>件・有無</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>第４次障がい者計画の定義による</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>測定：測れる（村の記録）</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>０件（第４次計画の基準値）</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>第３章に記載</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>３件</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>村の記録（進捗管理評価シート）</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>年１回（５月。前年度の実績）</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>第３章の目標値の扱いは中間見直しで決める</t>
-        </is>
-      </c>
-      <c r="R34" s="4" t="inlineStr">
-        <is>
-          <t>甲</t>
-        </is>
-      </c>
-      <c r="S34" s="4" t="inlineStr">
-        <is>
-          <t>照会Ｍ-95。令和7年度1件</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="72" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Ｋ-30</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>第４次計画</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>障がい者に配慮した公共施設トイレの設置率</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>成果</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>第３章 ⑥生活環境</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>％</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>第４次障がい者計画の定義による</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>測定：測れる（村の記録）</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>56.8％（第４次計画の基準値）</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>第３章に記載</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>100％</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>村の記録</t>
-        </is>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t>年１回（５月。前年度の実績）</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>第３章の目標値の扱いは中間見直しで決める</t>
-        </is>
-      </c>
-      <c r="R35" s="4" t="inlineStr">
-        <is>
-          <t>甲</t>
-        </is>
-      </c>
-      <c r="S35" s="4" t="inlineStr">
-        <is>
-          <t>照会Ｍ-95</t>
+      <c r="S35" s="9" t="inlineStr">
+        <is>
+          <t>Ｍ-24・Ｍ-25</t>
+        </is>
+      </c>
+      <c r="T35" s="9" t="inlineStr">
+        <is>
+          <t>95％以上・100％・100％</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4257,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>個別避難計画の策定件数</t>
+          <t>差別や偏見を感じている障がいがある人の割合</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -4187,12 +4267,12 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>第３章 ⑥生活環境</t>
+          <t>第３章 ①啓発・広報</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>件・有無</t>
+          <t>％</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -4202,12 +4282,12 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>測定：測れる（村の記録）</t>
+          <t>測定：測れる（参考値）</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>１件（第４次計画の基準値）</t>
+          <t>25.3％（第４次計画の基準値）</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -4227,12 +4307,12 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>10件</t>
+          <t>15％</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>村の記録</t>
+          <t>今回のアンケート（障がい者版）</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
@@ -4257,9 +4337,10 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
-          <t>照会Ｍ-41。村資料どうしで1件と実質0件の食い違いがあり、まず基準値を確定させる</t>
-        </is>
-      </c>
+          <t>調査の方法と集計が前回と異なるため参考値とする。正本に23.7％を記載済み</t>
+        </is>
+      </c>
+      <c r="T36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="72" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -4274,94 +4355,683 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
+          <t>特定健康診査の受診率</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>第３章 ②保健・医療</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>％</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>第４次障がい者計画の定義による</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>測定：測れる（村の記録）</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>51.3％（第４次計画の基準値）</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>第３章に記載</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>60％</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>村（国民健康保険）の記録</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>第３章の目標値の扱いは中間見直しで決める</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>甲</t>
+        </is>
+      </c>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>照会Ｍ-96。ただしこの指標は国保の被保険者全体のもので、障がいのある方の受診率ではないことを正本に注記済み</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Ｋ-33</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>第４次計画</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>現在利用している福祉サービスに満足している人の割合</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>成果</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>第３章 ③福祉</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>％</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>第４次障がい者計画の定義による</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>測定：測れる（参考値）</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>52％（第４次計画の基準値）</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>第３章に記載</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>60％</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>今回のアンケート（障がい者版）</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>第３章の目標値の扱いは中間見直しで決める</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>甲</t>
+        </is>
+      </c>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>分母の定義により39.4％とも61.9％とも読める。分母を決めてから評価する</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Ｋ-34</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>第４次計画</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>医療的ケア児の受入れ体制の整備</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>第３章 ④教育・育成</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>件・有無</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>第４次障がい者計画の定義による</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>測定：測れる（村の記録）</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>無（第４次計画の基準値）</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>第３章に記載</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>村の記録</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>第３章の目標値の扱いは中間見直しで決める</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>甲</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>照会Ｍ-95</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Ｋ-35</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>第４次計画</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>障がい者就労施設等からの物品調達件数</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>第３章 ⑤雇用・就業</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>件・有無</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>第４次障がい者計画の定義による</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>測定：測れる（村の記録）</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>０件（第４次計画の基準値）</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>第３章に記載</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>３件</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>村の記録（進捗管理評価シート）</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>第３章の目標値の扱いは中間見直しで決める</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>甲</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>照会Ｍ-95。令和7年度1件</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41" ht="72" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Ｋ-36</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>第４次計画</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>障がい者に配慮した公共施設トイレの設置率</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>体制</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>第３章 ⑥生活環境</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>％</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>第４次障がい者計画の定義による</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>測定：測れる（村の記録）</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>56.8％（第４次計画の基準値）</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>第３章に記載</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>100％</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>村の記録</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>第３章の目標値の扱いは中間見直しで決める</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>甲</t>
+        </is>
+      </c>
+      <c r="S41" s="4" t="inlineStr">
+        <is>
+          <t>照会Ｍ-95</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Ｋ-37</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>第４次計画</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>個別避難計画の策定件数</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>活動</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>第３章 ⑥生活環境</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>件・有無</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>第４次障がい者計画の定義による</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>測定：測れる（村の記録）</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>１件（第４次計画の基準値）</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>第３章に記載</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>10件</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>村の記録</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>年１回（５月。前年度の実績）</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>第３章の目標値の扱いは中間見直しで決める</t>
+        </is>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>甲</t>
+        </is>
+      </c>
+      <c r="S42" s="4" t="inlineStr">
+        <is>
+          <t>照会Ｍ-41。村資料どうしで1件と実質0件の食い違いがあり、まず基準値を確定させる</t>
+        </is>
+      </c>
+      <c r="T42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Ｋ-38</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>第４次計画</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
           <t>外出目的が趣味・スポーツ・グループ活動である人の割合</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>成果</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>第３章 ⑦スポーツ・文化</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>％</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>第４次障がい者計画の定義による</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>測定：測れない</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>28.1％（第４次計画の基準値）</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>第３章に記載</t>
         </is>
       </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="L43" s="4" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>40％</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>今回のアンケート（障がい者版）</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>年１回（５月。前年度の実績）</t>
         </is>
       </c>
-      <c r="P37" s="4" t="inlineStr">
+      <c r="P43" s="4" t="inlineStr">
         <is>
           <t>障がい福祉の担当（課名はＭ-134で確認中）</t>
         </is>
       </c>
-      <c r="Q37" s="4" t="inlineStr">
+      <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>第３章の目標値の扱いは中間見直しで決める</t>
         </is>
       </c>
-      <c r="R37" s="4" t="inlineStr">
+      <c r="R43" s="4" t="inlineStr">
         <is>
           <t>甲</t>
         </is>
       </c>
-      <c r="S37" s="4" t="inlineStr">
+      <c r="S43" s="4" t="inlineStr">
         <is>
           <t>村の生涯学習・スポーツ・文化の事業への障がいのある方の参加の実績と、理解促進研修・啓発事業の実施の実績で測る（Ｍ-111）。アンケートの問42（今後参加したいもの）は尺度が違うため、基準値28.1％と比べず参考値としてのみ用いる</t>
         </is>
       </c>
+      <c r="T43" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4439,7 +5109,8 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Ｋ-03 地域移行の意向確認の実施率【提案】</t>
+          <t>Ｋ-03 地域移行の意向確認の実施率【提案】
+Ｋ-28 地域生活の選択肢と体験の機会の提示率【提案】</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -4463,7 +5134,8 @@
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Ｋ-05 保健・医療・福祉の協議の場の開催回数
-Ｋ-06 心のサポーター養成研修の受講者数</t>
+Ｋ-06 心のサポーター養成研修の受講者数
+Ｋ-25 長期入院者の個別の退院支援の方針の作成率【提案】</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
@@ -4483,7 +5155,8 @@
         <is>
           <t>Ｋ-07 福祉施設から一般就労への移行者数
 Ｋ-08 就労定着支援事業の利用者数
-Ｋ-10 就労選択支援を経た方の進路決定率【提案】</t>
+Ｋ-10 就労選択支援を経た方の進路決定率【提案】
+Ｋ-26 一般就労した方の６か月・12か月後の就労継続率【提案】</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -4559,7 +5232,8 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Ｋ-19 計画相談支援のモニタリングの実施率【提案】</t>
+          <t>Ｋ-19 計画相談支援のモニタリングの実施率【提案】
+Ｋ-27 計画相談支援の月平均利用者数【提案】</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4620,12 +5294,14 @@
       <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Ｋ-22 重度の障がいのある方の受入れ確保率【提案】
-Ｋ-23 移動の希望に対し利用できなかった件数（冬季を含む）【提案】</t>
+Ｋ-23 移動の希望に対し利用できなかった件数（冬季を含む）【提案】
+Ｋ-30 必要量に対する確保率【提案】</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Ｋ-24 個別避難計画の作成率【提案】</t>
+          <t>Ｋ-24 個別避難計画の作成率【提案】
+Ｋ-29 見込量と実績の乖離の理由が記録されていない件数【提案】</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -4691,7 +5367,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>9指標（Ｋ-03・Ｋ-10・Ｋ-13・Ｋ-14・Ｋ-16・Ｋ-19・Ｋ-22・Ｋ-23・Ｋ-24）。採る場合は基準値と目標値を決める。見込量の置き直し（Ｍ-139）とあわせて決めるのがよい</t>
+          <t>15指標（Ｋ-03・Ｋ-10・Ｋ-13・Ｋ-14・Ｋ-16・Ｋ-19・Ｋ-22・Ｋ-23・Ｋ-24・Ｋ-25・Ｋ-26・Ｋ-27・Ｋ-28・Ｋ-29・Ｋ-30）。採る場合は基準値と目標値を決める。見込量の置き直し（Ｍ-139）とあわせて決めるのがよい</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_KPI定義票_様式案.xlsx
+++ b/output/北塩原村_KPI定義票_様式案.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -742,118 +742,130 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>０件・該当なしの扱い</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>分母が０の年度や、対象の方がいない年度の扱い（第３回のレビューによる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>照会・根拠</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>値や扱いを村に確かめている照会番号、正本の表</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>公表区分（案）</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>甲</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>実数を公表する（体制・回数・カ所数・研修の人数など、個人に結びつかないもの）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>乙</t>
+          <t>甲</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>実数を公表し、属性（障がいの種別・年齢・利用先）は併記しない（国・県へ報告する成果目標の人数など）</t>
+          <t>実数を公表する（体制・回数・カ所数・研修の人数など、個人に結びつかないもの）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>実数を公表し、属性（障がいの種別・年齢・利用先）は併記しない（国・県へ報告する成果目標の人数など）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>丙</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>村の内部の記録にとどめ、計画と公表には達成の有無又は「該当あり・なし」だけを書く（児童・医療的ケアなど、属性で個人が分かりうるもの。正本 第４章のＭ-76・Ｍ-77の考え方）</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>値の置き方</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>正本の値</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>正本 第４章の表にある基準値・目標値を写したもの。正本を直したら一覧も直す（生成のたびに照合）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>【提案】</t>
+          <t>正本の値</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>他ＡＩのレビュー（令和８年10月23日）の提案から足した指標。算定方法とデータの出所だけを置き、基準値・目標値は「村が決定」として空けている</t>
+          <t>正本 第４章の表にある基準値・目標値を写したもの。正本を直したら一覧も直す（生成のたびに照合）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>第４次計画</t>
+          <t>【提案】</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>第４次障がい者計画の8指標。値は第３章による。中間見直しで目標値を改める場合はここも改める</t>
+          <t>他ＡＩのレビュー（令和８年10月23日）の提案から足した指標。算定方法とデータの出所だけを置き、基準値・目標値は「村が決定」として空けている</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>第４次計画</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>第４次障がい者計画の8指標。値は第３章による。中間見直しで目標値を改める場合はここも改める</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>年次の点検評価との関係</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>定義票の「現状値」は第１章６の年次の点検評価の「実績」の欄に、「未達時の改善措置」は「令和９年度から令和11年度までの対応」の欄に当たる</t>
         </is>
@@ -874,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1156,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>国の基準（基準値の1.47倍）では０人となる。目標２人の扱いは村が決める</t>
+          <t>国の基準（基準値の1.47倍）では０人となる。目標２人の扱いは村が決める。利用者数は定着の成果そのものではないため、Ｋ-26（６か月・12か月後の就労継続率）と併せて見る</t>
         </is>
       </c>
     </row>
@@ -1169,16 +1181,34 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>照会・根拠</t>
+          <t>０件・該当なしの扱い</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
+          <t>０件・該当なしの扱い</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>照会・根拠</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>照会・根拠</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Ｍ-140</t>
         </is>
@@ -1195,7 +1225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1216,8 +1246,9 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="6" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1327,10 +1358,15 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
+          <t>０件・該当なしの扱い</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
           <t>照会・根拠</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>参考：レビューの目標案（Ｒ９・10・11）</t>
         </is>
@@ -1429,10 +1465,15 @@
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-94</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1525,8 +1566,13 @@
           <t>乙</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
       <c r="T7" s="4" t="inlineStr"/>
+      <c r="U7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -1621,10 +1667,15 @@
       </c>
       <c r="S8" s="9" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-94</t>
         </is>
       </c>
-      <c r="T8" s="9" t="inlineStr">
+      <c r="U8" s="9" t="inlineStr">
         <is>
           <t>100％・100％・100％</t>
         </is>
@@ -1723,10 +1774,15 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-119・Ｍ-93</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1819,8 +1875,13 @@
           <t>甲</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
       <c r="T10" s="4" t="inlineStr"/>
+      <c r="U10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="72" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1913,8 +1974,13 @@
           <t>甲</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
       <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="72" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -2009,10 +2075,15 @@
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-140</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr"/>
+      <c r="U12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="72" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -2097,7 +2168,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>国の基準（基準値の1.47倍）では０人となる。目標２人の扱いは村が決める</t>
+          <t>国の基準（基準値の1.47倍）では０人となる。目標２人の扱いは村が決める。利用者数は定着の成果そのものではないため、Ｋ-26（６か月・12か月後の就労継続率）と併せて見る</t>
         </is>
       </c>
       <c r="R13" s="4" t="inlineStr">
@@ -2107,10 +2178,15 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-140</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr"/>
+      <c r="U13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="72" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -2205,10 +2281,15 @@
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-21</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr"/>
+      <c r="U14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="72" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -2297,8 +2378,13 @@
           <t>丙</t>
         </is>
       </c>
-      <c r="S15" s="9" t="inlineStr"/>
-      <c r="T15" s="9" t="inlineStr">
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr"/>
+      <c r="U15" s="9" t="inlineStr">
         <is>
           <t>100％・100％・100％</t>
         </is>
@@ -2393,10 +2479,15 @@
       </c>
       <c r="S16" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-98</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr"/>
+      <c r="U16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="72" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -2485,8 +2576,13 @@
           <t>甲</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
       <c r="T17" s="4" t="inlineStr"/>
+      <c r="U17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="72" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
@@ -2521,12 +2617,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>分子：うち障がい児相談支援又は児童発達支援につながった児童数／分母：乳幼児健診等で発達の支援が必要とされた児童数</t>
+          <t>分子：うち必要な支援につながった児童数（障がい児相談支援・児童発達支援のほか、保健師の継続支援、保育所・幼稚園・学校での配慮、医療機関の受診を含む）／分母：乳幼児健診等で発達の支援が必要とされた児童数</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>同じ児童を年度をまたいで二重に数えない</t>
+          <t>同じ児童を年度をまたいで二重に数えない。つながった先ごとに内訳を取る</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
@@ -2581,10 +2677,15 @@
       </c>
       <c r="S18" s="9" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T18" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-76・Ｍ-77</t>
         </is>
       </c>
-      <c r="T18" s="9" t="inlineStr">
+      <c r="U18" s="9" t="inlineStr">
         <is>
           <t>100％・100％・100％（３か月以内の接続）</t>
         </is>
@@ -2681,8 +2782,13 @@
           <t>甲</t>
         </is>
       </c>
-      <c r="S19" s="9" t="inlineStr"/>
-      <c r="T19" s="9" t="inlineStr">
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T19" s="9" t="inlineStr"/>
+      <c r="U19" s="9" t="inlineStr">
         <is>
           <t>２・３・４</t>
         </is>
@@ -2775,8 +2881,13 @@
           <t>甲</t>
         </is>
       </c>
-      <c r="S20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
       <c r="T20" s="4" t="inlineStr"/>
+      <c r="U20" s="4" t="inlineStr"/>
     </row>
     <row r="21" ht="72" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -2869,8 +2980,13 @@
           <t>甲</t>
         </is>
       </c>
-      <c r="S21" s="9" t="inlineStr"/>
-      <c r="T21" s="9" t="inlineStr">
+      <c r="S21" s="9" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T21" s="9" t="inlineStr"/>
+      <c r="U21" s="9" t="inlineStr">
         <is>
           <t>０件・０件・０件</t>
         </is>
@@ -2965,10 +3081,15 @@
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-117</t>
         </is>
       </c>
-      <c r="T22" s="4" t="inlineStr"/>
+      <c r="U22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="72" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -3063,10 +3184,15 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
           <t>Ｍ-115</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr"/>
+      <c r="U23" s="4" t="inlineStr"/>
     </row>
     <row r="24" ht="72" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -3104,7 +3230,11 @@
           <t>分子：その年度に実施したモニタリングの回数／分母：支給決定で定めたモニタリングの回数</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>予定＝支給決定で定めたモニタリングの月。実施＝その月に行ったもの。延期（翌月以降に行ったもの）と中止（利用の終了・入院等）は分けて数え、中止は分母から除く</t>
+        </is>
+      </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
           <t>村が決定</t>
@@ -3157,10 +3287,15 @@
       </c>
       <c r="S24" s="9" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T24" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-115・Ｍ-136</t>
         </is>
       </c>
-      <c r="T24" s="9" t="inlineStr">
+      <c r="U24" s="9" t="inlineStr">
         <is>
           <t>100％・100％・100％</t>
         </is>
@@ -3253,8 +3388,13 @@
           <t>甲</t>
         </is>
       </c>
-      <c r="S25" s="4" t="inlineStr"/>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
       <c r="T25" s="4" t="inlineStr"/>
+      <c r="U25" s="4" t="inlineStr"/>
     </row>
     <row r="26" ht="72" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -3292,7 +3432,11 @@
           <t>分子：公表・更新している村内の対象事業所数／分母：村内の対象事業所数</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>対象事業所が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>―（新規）</t>
@@ -3343,8 +3487,13 @@
           <t>甲</t>
         </is>
       </c>
-      <c r="S26" s="4" t="inlineStr"/>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
       <c r="T26" s="4" t="inlineStr"/>
+      <c r="U26" s="4" t="inlineStr"/>
     </row>
     <row r="27" ht="72" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -3439,10 +3588,15 @@
       </c>
       <c r="S27" s="9" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T27" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-22・Ｍ-87</t>
         </is>
       </c>
-      <c r="T27" s="9" t="inlineStr">
+      <c r="U27" s="9" t="inlineStr">
         <is>
           <t>80％以上・90％以上・100％</t>
         </is>
@@ -3539,8 +3693,13 @@
           <t>甲</t>
         </is>
       </c>
-      <c r="S28" s="9" t="inlineStr"/>
-      <c r="T28" s="9" t="inlineStr">
+      <c r="S28" s="9" t="inlineStr">
+        <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T28" s="9" t="inlineStr"/>
+      <c r="U28" s="9" t="inlineStr">
         <is>
           <t>０件・０件・０件</t>
         </is>
@@ -3579,12 +3738,12 @@
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>分子：個別避難計画を作成した方の数／分母：避難行動要支援者名簿の掲載者のうち障がいのある方</t>
+          <t>分子：個別避難計画を作成した方の数／分母は２つに分けて出す。①全対象：避難行動要支援者名簿の掲載者のうち障がいのある方、②優先対象：①のうち村が優先度が高いと定めた方</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>更新した計画も数える（更新率は別に見る）。第４次計画の指標（個別避難計画の策定件数）と同じ記録から取る</t>
+          <t>目標も全対象と優先対象で分ける。更新した計画も数える（更新率は別に見る）。第４次計画の指標（個別避難計画の策定件数）と同じ記録から取る</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -3639,10 +3798,15 @@
       </c>
       <c r="S29" s="9" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T29" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-41・Ｍ-119</t>
         </is>
       </c>
-      <c r="T29" s="9" t="inlineStr">
+      <c r="U29" s="9" t="inlineStr">
         <is>
           <t>50％以上・75％以上・100％（優先対象者に対して）</t>
         </is>
@@ -3741,10 +3905,15 @@
       </c>
       <c r="S30" s="9" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T30" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-93・Ｍ-119</t>
         </is>
       </c>
-      <c r="T30" s="9" t="inlineStr">
+      <c r="U30" s="9" t="inlineStr">
         <is>
           <t>100％・100％・100％</t>
         </is>
@@ -3841,8 +4010,13 @@
           <t>丙</t>
         </is>
       </c>
-      <c r="S31" s="9" t="inlineStr"/>
+      <c r="S31" s="9" t="inlineStr">
+        <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
       <c r="T31" s="9" t="inlineStr"/>
+      <c r="U31" s="9" t="inlineStr"/>
     </row>
     <row r="32" ht="72" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
@@ -3937,10 +4111,15 @@
       </c>
       <c r="S32" s="9" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T32" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-136</t>
         </is>
       </c>
-      <c r="T32" s="9" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
     </row>
     <row r="33" ht="72" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
@@ -4035,10 +4214,15 @@
       </c>
       <c r="S33" s="9" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T33" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-94</t>
         </is>
       </c>
-      <c r="T33" s="9" t="inlineStr"/>
+      <c r="U33" s="9" t="inlineStr"/>
     </row>
     <row r="34" ht="72" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
@@ -4078,7 +4262,7 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>一定以上の幅（例：２割又は１人）は村が決める</t>
+          <t>一定以上の幅は村が決める（検討案：人数の差１人以上又は量の差２割以上）</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
@@ -4133,12 +4317,17 @@
       </c>
       <c r="S34" s="9" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T34" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-139</t>
         </is>
       </c>
-      <c r="T34" s="9" t="inlineStr">
-        <is>
-          <t>０件・０件・０件</t>
+      <c r="U34" s="9" t="inlineStr">
+        <is>
+          <t>０件・０件・０件（第３回：乖離の幅は人数差１人以上・量の差20％以上を検討案とする）</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4364,7 @@
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>分子：実際に確保できる量／分母：必要な量（同じ単位・期間）</t>
+          <t>分子：地理的・実質的に利用できる量（送迎の範囲、冬季の通所、障がいの特性への対応ができる事業所の空き）／分母：必要な量（同じ単位・期間）</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -4235,10 +4424,15 @@
       </c>
       <c r="S35" s="9" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T35" s="9" t="inlineStr">
+        <is>
           <t>Ｍ-24・Ｍ-25</t>
         </is>
       </c>
-      <c r="T35" s="9" t="inlineStr">
+      <c r="U35" s="9" t="inlineStr">
         <is>
           <t>95％以上・100％・100％</t>
         </is>
@@ -4337,10 +4531,15 @@
       </c>
       <c r="S36" s="4" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
           <t>調査の方法と集計が前回と異なるため参考値とする。正本に23.7％を記載済み</t>
         </is>
       </c>
-      <c r="T36" s="4" t="inlineStr"/>
+      <c r="U36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="72" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -4380,7 +4579,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>測定：測れる（村の記録）</t>
+          <t>測定：測れる（村の記録）。国保の被保険者全体の指標であり、障がいのある方の施策の直接の成果ではない。関連する地域保健の指標として位置づける</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -4435,10 +4634,15 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
           <t>照会Ｍ-96。ただしこの指標は国保の被保険者全体のもので、障がいのある方の受診率ではないことを正本に注記済み</t>
         </is>
       </c>
-      <c r="T37" s="4" t="inlineStr"/>
+      <c r="U37" s="4" t="inlineStr"/>
     </row>
     <row r="38" ht="72" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -4478,7 +4682,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>測定：測れる（参考値）</t>
+          <t>測定：測れる（参考値）。分母（回答者全体か、サービスを利用している回答者か）と、無回答・非利用者の扱いを固定してから再計算する（39.4％と61.9％の違いはこの分母の違いによる）</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -4533,10 +4737,15 @@
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
           <t>分母の定義により39.4％とも61.9％とも読める。分母を決めてから評価する</t>
         </is>
       </c>
-      <c r="T38" s="4" t="inlineStr"/>
+      <c r="U38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="72" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -4631,10 +4840,15 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
           <t>照会Ｍ-95</t>
         </is>
       </c>
-      <c r="T39" s="4" t="inlineStr"/>
+      <c r="U39" s="4" t="inlineStr"/>
     </row>
     <row r="40" ht="72" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -4729,10 +4943,15 @@
       </c>
       <c r="S40" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
           <t>照会Ｍ-95。令和7年度1件</t>
         </is>
       </c>
-      <c r="T40" s="4" t="inlineStr"/>
+      <c r="U40" s="4" t="inlineStr"/>
     </row>
     <row r="41" ht="72" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -4827,10 +5046,15 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
           <t>照会Ｍ-95</t>
         </is>
       </c>
-      <c r="T41" s="4" t="inlineStr"/>
+      <c r="U41" s="4" t="inlineStr"/>
     </row>
     <row r="42" ht="72" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -4925,10 +5149,15 @@
       </c>
       <c r="S42" s="4" t="inlineStr">
         <is>
+          <t>対象の方がいない年度も０として記録する（未記入と区別する）</t>
+        </is>
+      </c>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
           <t>照会Ｍ-41。村資料どうしで1件と実質0件の食い違いがあり、まず基準値を確定させる</t>
         </is>
       </c>
-      <c r="T42" s="4" t="inlineStr"/>
+      <c r="U42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="72" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -5023,15 +5252,20 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
+          <t>分母が０の年度は「該当なし」とし、達成・未達を判定しない</t>
+        </is>
+      </c>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
           <t>村の生涯学習・スポーツ・文化の事業への障がいのある方の参加の実績と、理解促進研修・啓発事業の実施の実績で測る（Ｍ-111）。アンケートの問42（今後参加したいもの）は尺度が違うため、基準値28.1％と比べず参考値としてのみ用いる</t>
         </is>
       </c>
-      <c r="T43" s="4" t="inlineStr"/>
+      <c r="U43" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
